--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/187.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/187.xlsx
@@ -426,13 +426,13 @@
         <v>-5.42820361259444</v>
       </c>
       <c r="E2">
-        <v>-10.06227132175114</v>
+        <v>-13.76199835822576</v>
       </c>
       <c r="F2">
-        <v>4.02511859479805</v>
+        <v>3.797872632991644</v>
       </c>
       <c r="G2">
-        <v>-13.5872480904024</v>
+        <v>-17.85274035374959</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.31271136735084</v>
       </c>
       <c r="E3">
-        <v>-10.7028194416621</v>
+        <v>-12.41093266651131</v>
       </c>
       <c r="F3">
-        <v>3.759111430711263</v>
+        <v>3.956667657720926</v>
       </c>
       <c r="G3">
-        <v>-14.43258265167314</v>
+        <v>-16.40854134660685</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.1479262126918</v>
       </c>
       <c r="E4">
-        <v>-10.32228724232355</v>
+        <v>-14.05924286361523</v>
       </c>
       <c r="F4">
-        <v>3.851173839281674</v>
+        <v>4.277580322190083</v>
       </c>
       <c r="G4">
-        <v>-13.7195143163329</v>
+        <v>-16.75038662371923</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.955188992299241</v>
       </c>
       <c r="E5">
-        <v>-12.24634527870253</v>
+        <v>-15.29853223139835</v>
       </c>
       <c r="F5">
-        <v>4.172229037283221</v>
+        <v>4.42902220035398</v>
       </c>
       <c r="G5">
-        <v>-12.77642596637856</v>
+        <v>-15.39108821220386</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.737455650968811</v>
       </c>
       <c r="E6">
-        <v>-12.10814078046244</v>
+        <v>-14.73479608760549</v>
       </c>
       <c r="F6">
-        <v>4.219775056276544</v>
+        <v>4.327669772883602</v>
       </c>
       <c r="G6">
-        <v>-12.70811948026678</v>
+        <v>-15.24716058961128</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.505436493434001</v>
       </c>
       <c r="E7">
-        <v>-12.12684790658813</v>
+        <v>-16.23517009582683</v>
       </c>
       <c r="F7">
-        <v>4.546599694928036</v>
+        <v>4.379460123730303</v>
       </c>
       <c r="G7">
-        <v>-11.91355213484076</v>
+        <v>-13.81151106632371</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.256709311172956</v>
       </c>
       <c r="E8">
-        <v>-13.18633421389669</v>
+        <v>-17.42222804440548</v>
       </c>
       <c r="F8">
-        <v>4.44763232856631</v>
+        <v>4.519071718705868</v>
       </c>
       <c r="G8">
-        <v>-11.6900770687578</v>
+        <v>-13.59445514804139</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.996656569311319</v>
       </c>
       <c r="E9">
-        <v>-14.29918405891165</v>
+        <v>-17.06400763650272</v>
       </c>
       <c r="F9">
-        <v>5.083761067326788</v>
+        <v>4.183373575810168</v>
       </c>
       <c r="G9">
-        <v>-10.68812390856968</v>
+        <v>-12.48504499019407</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.717613093422213</v>
       </c>
       <c r="E10">
-        <v>-14.30849007299741</v>
+        <v>-16.53626380412283</v>
       </c>
       <c r="F10">
-        <v>5.220108644410631</v>
+        <v>5.242937765181691</v>
       </c>
       <c r="G10">
-        <v>-9.76904032432059</v>
+        <v>-12.6181653368737</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.417163851611427</v>
       </c>
       <c r="E11">
-        <v>-15.0550271270579</v>
+        <v>-18.63037056796384</v>
       </c>
       <c r="F11">
-        <v>5.355868666599847</v>
+        <v>5.052862964916564</v>
       </c>
       <c r="G11">
-        <v>-9.425173959156492</v>
+        <v>-10.99055217521872</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.093412135976409</v>
       </c>
       <c r="E12">
-        <v>-15.75138416063939</v>
+        <v>-19.61419966002625</v>
       </c>
       <c r="F12">
-        <v>5.703224468739097</v>
+        <v>5.152991187714307</v>
       </c>
       <c r="G12">
-        <v>-8.799914533699882</v>
+        <v>-11.85121787288182</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.743456561417777</v>
       </c>
       <c r="E13">
-        <v>-17.00208075444783</v>
+        <v>-20.59888010520211</v>
       </c>
       <c r="F13">
-        <v>5.917575896981995</v>
+        <v>5.431298995646313</v>
       </c>
       <c r="G13">
-        <v>-7.925708704781158</v>
+        <v>-10.00196368737263</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.374745940421008</v>
       </c>
       <c r="E14">
-        <v>-18.20550460809019</v>
+        <v>-22.01343047403008</v>
       </c>
       <c r="F14">
-        <v>6.179508185748356</v>
+        <v>6.059637485008745</v>
       </c>
       <c r="G14">
-        <v>-8.109834626584343</v>
+        <v>-9.841749835999604</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.988249603071239</v>
       </c>
       <c r="E15">
-        <v>-19.01310813414412</v>
+        <v>-22.92801919851522</v>
       </c>
       <c r="F15">
-        <v>6.31470282492576</v>
+        <v>5.995904407853715</v>
       </c>
       <c r="G15">
-        <v>-7.573622255043049</v>
+        <v>-9.324510200943873</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.5903827262609</v>
       </c>
       <c r="E16">
-        <v>-19.48466266103684</v>
+        <v>-23.52314219565524</v>
       </c>
       <c r="F16">
-        <v>5.911285417085869</v>
+        <v>6.269510192922779</v>
       </c>
       <c r="G16">
-        <v>-6.329976096669357</v>
+        <v>-8.523758756450498</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.187584782909408</v>
       </c>
       <c r="E17">
-        <v>-20.51038466614422</v>
+        <v>-24.68587318186468</v>
       </c>
       <c r="F17">
-        <v>6.582301613457563</v>
+        <v>6.32156819006919</v>
       </c>
       <c r="G17">
-        <v>-6.521825521215662</v>
+        <v>-9.419704937925616</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.7840455487469942</v>
       </c>
       <c r="E18">
-        <v>-21.96884764742457</v>
+        <v>-24.57517916322119</v>
       </c>
       <c r="F18">
-        <v>6.796404399871737</v>
+        <v>6.434472168486783</v>
       </c>
       <c r="G18">
-        <v>-6.22321762411894</v>
+        <v>-8.529591937690693</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3940583607663016</v>
       </c>
       <c r="E19">
-        <v>-22.91164876497749</v>
+        <v>-25.71025475866579</v>
       </c>
       <c r="F19">
-        <v>6.845535708486415</v>
+        <v>6.574497110706278</v>
       </c>
       <c r="G19">
-        <v>-6.454634688950613</v>
+        <v>-7.739103184369059</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.03082797290976307</v>
       </c>
       <c r="E20">
-        <v>-22.00696381314713</v>
+        <v>-26.01817287729134</v>
       </c>
       <c r="F20">
-        <v>7.38281427512291</v>
+        <v>6.956594669512523</v>
       </c>
       <c r="G20">
-        <v>-5.757178886373578</v>
+        <v>-7.9006247012301</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.2857979502105739</v>
       </c>
       <c r="E21">
-        <v>-23.21290096986375</v>
+        <v>-25.14341661017767</v>
       </c>
       <c r="F21">
-        <v>7.072748412468598</v>
+        <v>7.18797252005231</v>
       </c>
       <c r="G21">
-        <v>-5.740669195769232</v>
+        <v>-7.940232068061941</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.530914971827901</v>
       </c>
       <c r="E22">
-        <v>-24.47149069386756</v>
+        <v>-27.5620700492004</v>
       </c>
       <c r="F22">
-        <v>7.268144464609601</v>
+        <v>6.975505701848784</v>
       </c>
       <c r="G22">
-        <v>-6.102587965758977</v>
+        <v>-7.515141468091824</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.6858177754166981</v>
       </c>
       <c r="E23">
-        <v>-24.97380261622038</v>
+        <v>-27.77012625900881</v>
       </c>
       <c r="F23">
-        <v>7.362178587044734</v>
+        <v>6.79279196667862</v>
       </c>
       <c r="G23">
-        <v>-5.18183255601256</v>
+        <v>-6.91788263680637</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.7307613170099797</v>
       </c>
       <c r="E24">
-        <v>-24.883251249963</v>
+        <v>-28.00185733092932</v>
       </c>
       <c r="F24">
-        <v>7.105678409568331</v>
+        <v>6.711080659971522</v>
       </c>
       <c r="G24">
-        <v>-4.956549932065156</v>
+        <v>-8.237886528043353</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.6556074436196613</v>
       </c>
       <c r="E25">
-        <v>-23.53415997291591</v>
+        <v>-28.98565925214769</v>
       </c>
       <c r="F25">
-        <v>7.107493336547424</v>
+        <v>6.804489218570056</v>
       </c>
       <c r="G25">
-        <v>-5.88367152088359</v>
+        <v>-8.5958856121146</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.4606313745058045</v>
       </c>
       <c r="E26">
-        <v>-25.05102668347318</v>
+        <v>-28.62906003793968</v>
       </c>
       <c r="F26">
-        <v>6.771459447997651</v>
+        <v>6.609039320427928</v>
       </c>
       <c r="G26">
-        <v>-5.13995084439524</v>
+        <v>-8.34351279401934</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.1487885673002125</v>
       </c>
       <c r="E27">
-        <v>-25.08005873033636</v>
+        <v>-28.63832076728536</v>
       </c>
       <c r="F27">
-        <v>6.928721445400788</v>
+        <v>6.538399701775666</v>
       </c>
       <c r="G27">
-        <v>-5.221929883584212</v>
+        <v>-7.541708596044475</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.2626723085705037</v>
       </c>
       <c r="E28">
-        <v>-25.90154202922379</v>
+        <v>-28.07971085606919</v>
       </c>
       <c r="F28">
-        <v>6.813684215115098</v>
+        <v>6.626121172431858</v>
       </c>
       <c r="G28">
-        <v>-4.465248421309615</v>
+        <v>-8.189009633701552</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.7525244944473104</v>
       </c>
       <c r="E29">
-        <v>-25.19013687651481</v>
+        <v>-27.6666234570895</v>
       </c>
       <c r="F29">
-        <v>6.624705339343454</v>
+        <v>6.634798297142551</v>
       </c>
       <c r="G29">
-        <v>-4.725738697067168</v>
+        <v>-7.024323296985017</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.295397233082563</v>
       </c>
       <c r="E30">
-        <v>-23.66734239348149</v>
+        <v>-28.49880754005705</v>
       </c>
       <c r="F30">
-        <v>6.416036247925152</v>
+        <v>6.713803050440163</v>
       </c>
       <c r="G30">
-        <v>-4.182256367521635</v>
+        <v>-7.054856458493715</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.858264149915432</v>
       </c>
       <c r="E31">
-        <v>-24.93315050505353</v>
+        <v>-27.61181533617466</v>
       </c>
       <c r="F31">
-        <v>6.797625437132542</v>
+        <v>6.514769225811395</v>
       </c>
       <c r="G31">
-        <v>-4.765048114800474</v>
+        <v>-7.182405157030756</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.415170204798921</v>
       </c>
       <c r="E32">
-        <v>-23.39787101918106</v>
+        <v>-27.87444418624951</v>
       </c>
       <c r="F32">
-        <v>7.004197701918801</v>
+        <v>6.392032017364837</v>
       </c>
       <c r="G32">
-        <v>-5.201579960154312</v>
+        <v>-8.498148376158696</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.938314816282554</v>
       </c>
       <c r="E33">
-        <v>-23.0785547314782</v>
+        <v>-25.99579315874544</v>
       </c>
       <c r="F33">
-        <v>6.554057802161616</v>
+        <v>6.191617201177806</v>
       </c>
       <c r="G33">
-        <v>-5.242266564831955</v>
+        <v>-6.776336951729291</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.405676612187169</v>
       </c>
       <c r="E34">
-        <v>-23.23540295720787</v>
+        <v>-27.59814387314551</v>
       </c>
       <c r="F34">
-        <v>6.522638660505213</v>
+        <v>6.504459300301884</v>
       </c>
       <c r="G34">
-        <v>-5.349044900655608</v>
+        <v>-7.736537511576124</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.805922573237201</v>
       </c>
       <c r="E35">
-        <v>-22.87590099116094</v>
+        <v>-24.22275520204825</v>
       </c>
       <c r="F35">
-        <v>7.009927549920861</v>
+        <v>5.924610718658377</v>
       </c>
       <c r="G35">
-        <v>-4.872465385913206</v>
+        <v>-7.876950990078772</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.128708066066368</v>
       </c>
       <c r="E36">
-        <v>-23.08604029901288</v>
+        <v>-25.77453191873066</v>
       </c>
       <c r="F36">
-        <v>6.643967954392944</v>
+        <v>5.959179851380589</v>
       </c>
       <c r="G36">
-        <v>-5.691097086864185</v>
+        <v>-7.386295035703389</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.378634948675582</v>
       </c>
       <c r="E37">
-        <v>-21.17015615821774</v>
+        <v>-24.02454389473252</v>
       </c>
       <c r="F37">
-        <v>6.602636397411806</v>
+        <v>6.305786560621836</v>
       </c>
       <c r="G37">
-        <v>-4.823184605015616</v>
+        <v>-8.379750025492202</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.561960988563814</v>
       </c>
       <c r="E38">
-        <v>-20.93288676258585</v>
+        <v>-25.12199692812139</v>
       </c>
       <c r="F38">
-        <v>6.458865990702297</v>
+        <v>6.337804343114275</v>
       </c>
       <c r="G38">
-        <v>-5.820963167278715</v>
+        <v>-8.417533281731904</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.690014209443523</v>
       </c>
       <c r="E39">
-        <v>-19.66596464640793</v>
+        <v>-24.60452367479089</v>
       </c>
       <c r="F39">
-        <v>6.634144226599473</v>
+        <v>6.119629848791506</v>
       </c>
       <c r="G39">
-        <v>-6.444957964339324</v>
+        <v>-8.104266288987288</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.781005161088445</v>
       </c>
       <c r="E40">
-        <v>-20.47104128396558</v>
+        <v>-22.66661756489646</v>
       </c>
       <c r="F40">
-        <v>6.641207554982334</v>
+        <v>6.236784493886139</v>
       </c>
       <c r="G40">
-        <v>-6.552100460172296</v>
+        <v>-8.26660882114207</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.845471203578573</v>
       </c>
       <c r="E41">
-        <v>-19.82610507274118</v>
+        <v>-24.16701421548784</v>
       </c>
       <c r="F41">
-        <v>6.912732350478511</v>
+        <v>6.103292338567832</v>
       </c>
       <c r="G41">
-        <v>-6.041723586019476</v>
+        <v>-8.119627220289507</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.9035439391347</v>
       </c>
       <c r="E42">
-        <v>-19.8211554506508</v>
+        <v>-22.09655061444087</v>
       </c>
       <c r="F42">
-        <v>6.703586563579663</v>
+        <v>6.513418324665524</v>
       </c>
       <c r="G42">
-        <v>-5.776575372688168</v>
+        <v>-7.996958265877352</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.965200793083249</v>
       </c>
       <c r="E43">
-        <v>-18.8293109595948</v>
+        <v>-22.08461355695665</v>
       </c>
       <c r="F43">
-        <v>6.861770277825586</v>
+        <v>6.498224250112798</v>
       </c>
       <c r="G43">
-        <v>-6.211670441277962</v>
+        <v>-8.316783449335263</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.039302986821751</v>
       </c>
       <c r="E44">
-        <v>-17.74529390858669</v>
+        <v>-21.66147294567994</v>
       </c>
       <c r="F44">
-        <v>7.155371933782989</v>
+        <v>6.477857792040247</v>
       </c>
       <c r="G44">
-        <v>-6.320829059344351</v>
+        <v>-8.555715452541083</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.133991964857208</v>
       </c>
       <c r="E45">
-        <v>-17.51349038108206</v>
+        <v>-21.20462237389012</v>
       </c>
       <c r="F45">
-        <v>6.88103130916916</v>
+        <v>6.70554244038523</v>
       </c>
       <c r="G45">
-        <v>-6.465244987403977</v>
+        <v>-8.018470190791536</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.242825074006375</v>
       </c>
       <c r="E46">
-        <v>-16.74696917122572</v>
+        <v>-20.07556059192771</v>
       </c>
       <c r="F46">
-        <v>7.118203939653541</v>
+        <v>6.440664458616152</v>
       </c>
       <c r="G46">
-        <v>-7.143668463675743</v>
+        <v>-7.833774855155597</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.369074136877935</v>
       </c>
       <c r="E47">
-        <v>-16.45022279797709</v>
+        <v>-21.52552362749567</v>
       </c>
       <c r="F47">
-        <v>6.928167148330385</v>
+        <v>6.389862340260685</v>
       </c>
       <c r="G47">
-        <v>-7.085959033835168</v>
+        <v>-9.857491480038838</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.502937080304617</v>
       </c>
       <c r="E48">
-        <v>-15.21787105237372</v>
+        <v>-19.15013522914222</v>
       </c>
       <c r="F48">
-        <v>7.016937032302597</v>
+        <v>6.104294824412306</v>
       </c>
       <c r="G48">
-        <v>-7.430457713197267</v>
+        <v>-8.836482819726672</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.637688729969236</v>
       </c>
       <c r="E49">
-        <v>-14.53216951813228</v>
+        <v>-18.82125027586115</v>
       </c>
       <c r="F49">
-        <v>6.706546509935619</v>
+        <v>6.504688937659623</v>
       </c>
       <c r="G49">
-        <v>-7.304385517970742</v>
+        <v>-9.061987250225208</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.772185297512148</v>
       </c>
       <c r="E50">
-        <v>-14.42044300741503</v>
+        <v>-19.32402863103676</v>
       </c>
       <c r="F50">
-        <v>7.297178545157353</v>
+        <v>6.496976289851432</v>
       </c>
       <c r="G50">
-        <v>-6.552093839081218</v>
+        <v>-8.334256508691537</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.895870650663437</v>
       </c>
       <c r="E51">
-        <v>-14.62547419658632</v>
+        <v>-18.49824328184204</v>
       </c>
       <c r="F51">
-        <v>6.961493071908976</v>
+        <v>6.81042969945887</v>
       </c>
       <c r="G51">
-        <v>-6.856084683224795</v>
+        <v>-9.880360728624124</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.016426363505531</v>
       </c>
       <c r="E52">
-        <v>-12.60084780944499</v>
+        <v>-19.07587731236444</v>
       </c>
       <c r="F52">
-        <v>6.951384277050726</v>
+        <v>6.377116675053228</v>
       </c>
       <c r="G52">
-        <v>-6.684224332644609</v>
+        <v>-9.534157118309301</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.133446190419979</v>
       </c>
       <c r="E53">
-        <v>-13.24678934189909</v>
+        <v>-17.54937400911884</v>
       </c>
       <c r="F53">
-        <v>6.965840344646858</v>
+        <v>6.249498484975287</v>
       </c>
       <c r="G53">
-        <v>-6.931972318621508</v>
+        <v>-8.544383455160158</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.250570558016936</v>
       </c>
       <c r="E54">
-        <v>-12.17623544411578</v>
+        <v>-17.79076884457171</v>
       </c>
       <c r="F54">
-        <v>7.120467055406704</v>
+        <v>6.54695488113087</v>
       </c>
       <c r="G54">
-        <v>-7.940500222250622</v>
+        <v>-9.379965149272206</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.378159597982695</v>
       </c>
       <c r="E55">
-        <v>-12.44861862720315</v>
+        <v>-16.982698885695</v>
       </c>
       <c r="F55">
-        <v>7.008799951309069</v>
+        <v>6.235745582805611</v>
       </c>
       <c r="G55">
-        <v>-7.076464389228538</v>
+        <v>-8.891937768055003</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.512083680992152</v>
       </c>
       <c r="E56">
-        <v>-10.81860346509022</v>
+        <v>-16.69669858126657</v>
       </c>
       <c r="F56">
-        <v>7.268198310610726</v>
+        <v>6.450500856056946</v>
       </c>
       <c r="G56">
-        <v>-7.060487696456016</v>
+        <v>-9.37821718122747</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.662438481549193</v>
       </c>
       <c r="E57">
-        <v>-11.3485843636299</v>
+        <v>-15.31586722989971</v>
       </c>
       <c r="F57">
-        <v>6.963304831476239</v>
+        <v>6.455891790993102</v>
       </c>
       <c r="G57">
-        <v>-7.619549453309359</v>
+        <v>-8.808230624094533</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.826488658270737</v>
       </c>
       <c r="E58">
-        <v>-12.20145904433851</v>
+        <v>-15.12102510724569</v>
       </c>
       <c r="F58">
-        <v>6.787538814157108</v>
+        <v>6.307793116016698</v>
       </c>
       <c r="G58">
-        <v>-7.340679028717772</v>
+        <v>-9.837250804611735</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.999463334222386</v>
       </c>
       <c r="E59">
-        <v>-11.31364718666072</v>
+        <v>-14.82493989120217</v>
       </c>
       <c r="F59">
-        <v>7.127394185080836</v>
+        <v>6.608602217595267</v>
       </c>
       <c r="G59">
-        <v>-7.964908874511668</v>
+        <v>-8.65392940705464</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.182111110374512</v>
       </c>
       <c r="E60">
-        <v>-10.41788332862547</v>
+        <v>-14.54069210621471</v>
       </c>
       <c r="F60">
-        <v>6.696847894909467</v>
+        <v>5.995036537012053</v>
       </c>
       <c r="G60">
-        <v>-8.014100270679698</v>
+        <v>-8.510745001935623</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.358710748516109</v>
       </c>
       <c r="E61">
-        <v>-9.577348739587771</v>
+        <v>-15.06521166510115</v>
       </c>
       <c r="F61">
-        <v>6.721455517423566</v>
+        <v>6.154284501633152</v>
       </c>
       <c r="G61">
-        <v>-7.957112539766684</v>
+        <v>-10.3603434841809</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.528472513296169</v>
       </c>
       <c r="E62">
-        <v>-9.724972463763818</v>
+        <v>-13.95031947830874</v>
       </c>
       <c r="F62">
-        <v>6.794906214075732</v>
+        <v>6.383573444070475</v>
       </c>
       <c r="G62">
-        <v>-7.539639505082431</v>
+        <v>-9.039382845283065</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.679499616199861</v>
       </c>
       <c r="E63">
-        <v>-9.302751132710656</v>
+        <v>-14.29412575344508</v>
       </c>
       <c r="F63">
-        <v>6.765916477293612</v>
+        <v>6.347181465839592</v>
       </c>
       <c r="G63">
-        <v>-7.524612938879679</v>
+        <v>-9.290795605171935</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.800116938468243</v>
       </c>
       <c r="E64">
-        <v>-9.287521874622861</v>
+        <v>-11.89636216501973</v>
       </c>
       <c r="F64">
-        <v>6.733689645620336</v>
+        <v>6.026848437735486</v>
       </c>
       <c r="G64">
-        <v>-8.152530732404324</v>
+        <v>-9.414269022150133</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.888043487443785</v>
       </c>
       <c r="E65">
-        <v>-8.89904673187486</v>
+        <v>-12.71560839774738</v>
       </c>
       <c r="F65">
-        <v>6.376472106745645</v>
+        <v>6.080152811437347</v>
       </c>
       <c r="G65">
-        <v>-8.569626364897101</v>
+        <v>-9.56345875687739</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.928521142517633</v>
       </c>
       <c r="E66">
-        <v>-9.360815226437005</v>
+        <v>-12.96214757967297</v>
       </c>
       <c r="F66">
-        <v>6.418989859457447</v>
+        <v>5.567073271188767</v>
       </c>
       <c r="G66">
-        <v>-7.827951605552019</v>
+        <v>-9.839611223581235</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.924133349586633</v>
       </c>
       <c r="E67">
-        <v>-8.660332753034524</v>
+        <v>-12.77459177169728</v>
       </c>
       <c r="F67">
-        <v>6.458536579871886</v>
+        <v>5.616648017459768</v>
       </c>
       <c r="G67">
-        <v>-8.045351820570419</v>
+        <v>-9.479768165644614</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.869939165885596</v>
       </c>
       <c r="E68">
-        <v>-8.480891970480586</v>
+        <v>-12.5259921340982</v>
       </c>
       <c r="F68">
-        <v>6.570534678505848</v>
+        <v>5.813954018934792</v>
       </c>
       <c r="G68">
-        <v>-7.959171699092111</v>
+        <v>-9.492384654694776</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.762798078561687</v>
       </c>
       <c r="E69">
-        <v>-9.013780149333195</v>
+        <v>-12.44883599395551</v>
       </c>
       <c r="F69">
-        <v>6.026949794914074</v>
+        <v>5.411024392516857</v>
       </c>
       <c r="G69">
-        <v>-7.677573384976164</v>
+        <v>-10.14235068151097</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.608489891464632</v>
       </c>
       <c r="E70">
-        <v>-7.909326095128464</v>
+        <v>-12.95948936543046</v>
       </c>
       <c r="F70">
-        <v>5.781752526556161</v>
+        <v>5.406076895237024</v>
       </c>
       <c r="G70">
-        <v>-8.027514601204826</v>
+        <v>-10.34411518994739</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.401467341207248</v>
       </c>
       <c r="E71">
-        <v>-8.163509341179001</v>
+        <v>-12.13445574292101</v>
       </c>
       <c r="F71">
-        <v>6.341728766372734</v>
+        <v>5.306411114566589</v>
       </c>
       <c r="G71">
-        <v>-8.137934537121676</v>
+        <v>-9.808690728244441</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.152439722585845</v>
       </c>
       <c r="E72">
-        <v>-7.614943585311837</v>
+        <v>-11.91068119983198</v>
       </c>
       <c r="F72">
-        <v>5.379302763030605</v>
+        <v>5.179085910083003</v>
       </c>
       <c r="G72">
-        <v>-6.912370578483483</v>
+        <v>-9.305616917551253</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.865205110510973</v>
       </c>
       <c r="E73">
-        <v>-8.559347782663474</v>
+        <v>-11.2800368525758</v>
       </c>
       <c r="F73">
-        <v>5.735463970059698</v>
+        <v>5.095743386283003</v>
       </c>
       <c r="G73">
-        <v>-6.771106289777243</v>
+        <v>-9.431573243683903</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.545955096399246</v>
       </c>
       <c r="E74">
-        <v>-8.2493510944684</v>
+        <v>-12.05235450916195</v>
       </c>
       <c r="F74">
-        <v>5.542801394328742</v>
+        <v>4.963412087400713</v>
       </c>
       <c r="G74">
-        <v>-7.104809280135778</v>
+        <v>-9.858646860432044</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.208392436405201</v>
       </c>
       <c r="E75">
-        <v>-7.749176611847202</v>
+        <v>-11.53543825813439</v>
       </c>
       <c r="F75">
-        <v>5.533552551782576</v>
+        <v>4.79654332991452</v>
       </c>
       <c r="G75">
-        <v>-7.161810253230949</v>
+        <v>-9.131813276739516</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.853983917202697</v>
       </c>
       <c r="E76">
-        <v>-8.263244452723933</v>
+        <v>-12.8288021340431</v>
       </c>
       <c r="F76">
-        <v>5.110094929288715</v>
+        <v>4.695477553214837</v>
       </c>
       <c r="G76">
-        <v>-6.502051632709595</v>
+        <v>-8.887514879214537</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.496902460141248</v>
       </c>
       <c r="E77">
-        <v>-9.990331983665286</v>
+        <v>-14.2434838286173</v>
       </c>
       <c r="F77">
-        <v>5.25925943834621</v>
+        <v>5.130679938777597</v>
       </c>
       <c r="G77">
-        <v>-6.358085938843309</v>
+        <v>-8.51979603343999</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.141633478396078</v>
       </c>
       <c r="E78">
-        <v>-9.684755086101697</v>
+        <v>-14.56484245809762</v>
       </c>
       <c r="F78">
-        <v>5.032456914196127</v>
+        <v>4.673109290865169</v>
       </c>
       <c r="G78">
-        <v>-6.45864707014421</v>
+        <v>-8.48159564846234</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.79217105219634</v>
       </c>
       <c r="E79">
-        <v>-8.654355167344399</v>
+        <v>-13.61778457497749</v>
       </c>
       <c r="F79">
-        <v>5.18213929508797</v>
+        <v>4.409314563942252</v>
       </c>
       <c r="G79">
-        <v>-6.838899641330438</v>
+        <v>-8.594127712433247</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.459747300204245</v>
       </c>
       <c r="E80">
-        <v>-10.07114260233216</v>
+        <v>-15.56117466689521</v>
       </c>
       <c r="F80">
-        <v>4.882644669419217</v>
+        <v>5.021348800905234</v>
       </c>
       <c r="G80">
-        <v>-6.0662315546467</v>
+        <v>-8.045825228582535</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.143600376143665</v>
       </c>
       <c r="E81">
-        <v>-11.52125960601638</v>
+        <v>-14.2425373775497</v>
       </c>
       <c r="F81">
-        <v>4.928231644195141</v>
+        <v>4.258667706147905</v>
       </c>
       <c r="G81">
-        <v>-5.851440049513246</v>
+        <v>-8.429080464572881</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.85550241664144</v>
       </c>
       <c r="E82">
-        <v>-10.13667867817117</v>
+        <v>-15.54878476201023</v>
       </c>
       <c r="F82">
-        <v>5.013830948924643</v>
+        <v>4.378353113295411</v>
       </c>
       <c r="G82">
-        <v>-6.282367141269098</v>
+        <v>-7.149693656557217</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.602726007149061</v>
       </c>
       <c r="E83">
-        <v>-12.75573973440335</v>
+        <v>-15.8359896405247</v>
       </c>
       <c r="F83">
-        <v>5.045167737873443</v>
+        <v>3.92440915192934</v>
       </c>
       <c r="G83">
-        <v>-4.618957050697976</v>
+        <v>-6.721030977950226</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.390316724702311</v>
       </c>
       <c r="E84">
-        <v>-13.09115927567749</v>
+        <v>-15.9692988583625</v>
       </c>
       <c r="F84">
-        <v>4.74769075354096</v>
+        <v>4.184486921068721</v>
       </c>
       <c r="G84">
-        <v>-4.407350290373301</v>
+        <v>-7.637565442134073</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.235717886039409</v>
       </c>
       <c r="E85">
-        <v>-13.29412095222726</v>
+        <v>-18.33430799429036</v>
       </c>
       <c r="F85">
-        <v>4.674376255597521</v>
+        <v>4.758554976120874</v>
       </c>
       <c r="G85">
-        <v>-3.954000873679965</v>
+        <v>-8.187006753650294</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.144237645145636</v>
       </c>
       <c r="E86">
-        <v>-15.15460827048657</v>
+        <v>-19.00771472160098</v>
       </c>
       <c r="F86">
-        <v>4.904485557699042</v>
+        <v>3.725505191185638</v>
       </c>
       <c r="G86">
-        <v>-3.54788963128649</v>
+        <v>-6.043332511151561</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.130225383340395</v>
       </c>
       <c r="E87">
-        <v>-17.05092034662055</v>
+        <v>-21.77157373422843</v>
       </c>
       <c r="F87">
-        <v>4.168090813726177</v>
+        <v>3.900530034136344</v>
       </c>
       <c r="G87">
-        <v>-3.895377733270551</v>
+        <v>-6.334869082976399</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.206327782782832</v>
       </c>
       <c r="E88">
-        <v>-17.5889664573679</v>
+        <v>-21.80076880615588</v>
       </c>
       <c r="F88">
-        <v>4.35400680225736</v>
+        <v>3.166008814261444</v>
       </c>
       <c r="G88">
-        <v>-3.744244708311743</v>
+        <v>-6.430914630161736</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.37247909518669</v>
       </c>
       <c r="E89">
-        <v>-19.07639355840131</v>
+        <v>-23.19967329728735</v>
       </c>
       <c r="F89">
-        <v>4.025105925150727</v>
+        <v>3.566718084985933</v>
       </c>
       <c r="G89">
-        <v>-3.583193288917278</v>
+        <v>-6.552573868184412</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.642633307548306</v>
       </c>
       <c r="E90">
-        <v>-19.48527853350188</v>
+        <v>-23.95647187344922</v>
       </c>
       <c r="F90">
-        <v>3.700910238318864</v>
+        <v>3.552775138106404</v>
       </c>
       <c r="G90">
-        <v>-3.542023344590902</v>
+        <v>-6.072796366451075</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.012463838731096</v>
       </c>
       <c r="E91">
-        <v>-22.5234136313519</v>
+        <v>-25.60770293628809</v>
       </c>
       <c r="F91">
-        <v>3.787923792430853</v>
+        <v>3.176371002066164</v>
       </c>
       <c r="G91">
-        <v>-3.846424696381348</v>
+        <v>-5.377194469376031</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.478942525773592</v>
       </c>
       <c r="E92">
-        <v>-24.10885502380733</v>
+        <v>-29.08690234553718</v>
       </c>
       <c r="F92">
-        <v>3.177980047276251</v>
+        <v>2.817222925680553</v>
       </c>
       <c r="G92">
-        <v>-3.545357063948948</v>
+        <v>-5.57188434199503</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.039267675342179</v>
       </c>
       <c r="E93">
-        <v>-26.14097603543135</v>
+        <v>-29.8878920353029</v>
       </c>
       <c r="F93">
-        <v>2.927768765990057</v>
+        <v>2.715026382957245</v>
       </c>
       <c r="G93">
-        <v>-2.950127597079067</v>
+        <v>-5.613196639779595</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.668992906711377</v>
       </c>
       <c r="E94">
-        <v>-27.67353843689921</v>
+        <v>-32.71719202581518</v>
       </c>
       <c r="F94">
-        <v>2.460836832411467</v>
+        <v>2.193930123364711</v>
       </c>
       <c r="G94">
-        <v>-3.508126668814304</v>
+        <v>-4.787146006275109</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.358588905274944</v>
       </c>
       <c r="E95">
-        <v>-30.09625844558083</v>
+        <v>-33.92381524634397</v>
       </c>
       <c r="F95">
-        <v>2.665484894510468</v>
+        <v>2.261734908428335</v>
       </c>
       <c r="G95">
-        <v>-3.689120814537338</v>
+        <v>-6.117293409044419</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.086108035199525</v>
       </c>
       <c r="E96">
-        <v>-32.68733806091961</v>
+        <v>-35.28398996352484</v>
       </c>
       <c r="F96">
-        <v>2.505669963171643</v>
+        <v>1.768511872947536</v>
       </c>
       <c r="G96">
-        <v>-3.249202281096826</v>
+        <v>-5.095443870165278</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.821243467280294</v>
       </c>
       <c r="E97">
-        <v>-34.4879498958495</v>
+        <v>-38.34498479816557</v>
       </c>
       <c r="F97">
-        <v>1.987991340944627</v>
+        <v>2.144081395970339</v>
       </c>
       <c r="G97">
-        <v>-4.64069740325437</v>
+        <v>-5.782322479744343</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.561379218547701</v>
       </c>
       <c r="E98">
-        <v>-37.06579278166387</v>
+        <v>-39.9466018997764</v>
       </c>
       <c r="F98">
-        <v>1.91648226774479</v>
+        <v>2.157420950896086</v>
       </c>
       <c r="G98">
-        <v>-3.307087169850983</v>
+        <v>-6.179412485543303</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.26234910825281</v>
       </c>
       <c r="E99">
-        <v>-39.77179374613231</v>
+        <v>-43.13425135970066</v>
       </c>
       <c r="F99">
-        <v>1.40940338920981</v>
+        <v>1.202992662426925</v>
       </c>
       <c r="G99">
-        <v>-3.375536009420954</v>
+        <v>-5.443484833254397</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.949870913214838</v>
       </c>
       <c r="E100">
-        <v>-42.06174342538304</v>
+        <v>-44.31742840605474</v>
       </c>
       <c r="F100">
-        <v>1.148828336412981</v>
+        <v>1.704474724256742</v>
       </c>
       <c r="G100">
-        <v>-2.594320094154817</v>
+        <v>-5.746366644642318</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.57241933463627</v>
       </c>
       <c r="E101">
-        <v>-44.01365836962021</v>
+        <v>-46.14531297569582</v>
       </c>
       <c r="F101">
-        <v>1.348020531633293</v>
+        <v>1.310105028311757</v>
       </c>
       <c r="G101">
-        <v>-3.432715751975246</v>
+        <v>-5.422078845797469</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.20183597457095</v>
       </c>
       <c r="E102">
-        <v>-46.24023205513359</v>
+        <v>-49.57601469255976</v>
       </c>
       <c r="F102">
-        <v>1.059939674497111</v>
+        <v>0.3070371719146626</v>
       </c>
       <c r="G102">
-        <v>-3.96651804636395</v>
+        <v>-6.508864735429415</v>
       </c>
     </row>
   </sheetData>
